--- a/upload_excel/KV_Test.xlsx
+++ b/upload_excel/KV_Test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CNXK\Downloads\tagging\unpacktoolgit\upload_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyuns\Downloads\unpacktool\unpacktool\upload_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5797097A-59E4-4B4A-B42B-E890AB12BDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1323619-D61A-44D8-9AE5-588E200C9AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D524A933-36B5-41C2-8BA2-68E0D1C505E5}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{D524A933-36B5-41C2-8BA2-68E0D1C505E5}"/>
   </bookViews>
   <sheets>
     <sheet name="TEST" sheetId="3" r:id="rId1"/>
@@ -187,7 +187,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="206">
   <si>
     <r>
       <t>[</t>
@@ -954,276 +954,12 @@
     <t>an-la</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
-  <si>
-    <t>SG</t>
-  </si>
-  <si>
-    <t>AU</t>
-  </si>
-  <si>
-    <t>NZ</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>TH</t>
-  </si>
-  <si>
-    <t>MM</t>
-  </si>
-  <si>
-    <t>VN</t>
-  </si>
-  <si>
-    <t>MY</t>
-  </si>
-  <si>
-    <t>PH</t>
-  </si>
-  <si>
-    <t>JP</t>
-  </si>
-  <si>
-    <t>CN</t>
-  </si>
-  <si>
-    <t>HK</t>
-  </si>
-  <si>
-    <t>HK_EN</t>
-  </si>
-  <si>
-    <t>TW</t>
-  </si>
-  <si>
-    <t>IN</t>
-  </si>
-  <si>
-    <t>PK</t>
-  </si>
-  <si>
-    <t>BD</t>
-  </si>
-  <si>
-    <t>RU</t>
-  </si>
-  <si>
-    <t>AZ</t>
-  </si>
-  <si>
-    <t>UA</t>
-  </si>
-  <si>
-    <t>KZ_RU</t>
-  </si>
-  <si>
-    <t>KZ_KZ</t>
-  </si>
-  <si>
-    <t>UZ_RU</t>
-  </si>
-  <si>
-    <t>UZ_UZ</t>
-  </si>
-  <si>
-    <t>MN</t>
-  </si>
-  <si>
-    <t>AE</t>
-  </si>
-  <si>
-    <t>AE_AR</t>
-  </si>
-  <si>
-    <t>SA_EN</t>
-  </si>
-  <si>
-    <t>TR</t>
-  </si>
-  <si>
-    <t>LEVANT</t>
-  </si>
-  <si>
-    <t>LB</t>
-  </si>
-  <si>
-    <t>N_AFRICA</t>
-  </si>
-  <si>
-    <t>AFRICA_EN</t>
-  </si>
-  <si>
-    <t>AFRICA_FR</t>
-  </si>
-  <si>
-    <t>AFRICA_PT</t>
-  </si>
-  <si>
-    <t>ZA</t>
-  </si>
-  <si>
-    <t>IL</t>
-  </si>
-  <si>
-    <t>PS</t>
-  </si>
-  <si>
-    <t>SA</t>
-  </si>
-  <si>
-    <t>IRAN</t>
-  </si>
-  <si>
-    <t>LEVANT_AR</t>
-  </si>
-  <si>
-    <t>IQ_AR</t>
-  </si>
-  <si>
-    <t>IQ_KU</t>
-  </si>
-  <si>
-    <t>EG</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/sg.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/au.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/nz.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/id.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/th.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/mm.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/vn.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/my.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/ph.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/jp.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com.cn/cn.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/hk.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/hk_en.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/tw.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/in.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/pk.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/bd.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/ru.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/az.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-eu-author.samsung.com/content/samsung/ua.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/kz_ru.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/kz_kz.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/uz_ru.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/uz_uz.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/mn.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/ae.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/ae_ar.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/sa_en.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/tr.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/levant.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/lb.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/n_africa.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/africa_en.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/africa_fr.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/africa_pt.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/za.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/il.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/ps.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/sa.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/iran.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/levant_ar.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/iq_ar.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/iq_ku.html?wcmmode=disabled</t>
-  </si>
-  <si>
-    <t>https://p6-ap-author.samsung.com/content/samsung/eg.html?wcmmode=disabled</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1364,24 +1100,6 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1573,18 +1291,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1699,29 +1414,19 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="1" xr:uid="{94B65803-FEB7-4F70-81B3-C911D58CD782}"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="7">
     <dxf>
@@ -2127,34 +1832,34 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P59"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="14.4" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:P45"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.19921875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.69921875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="33.3984375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="13.69921875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="3.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.75" style="4" customWidth="1"/>
+    <col min="3" max="3" width="33.375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="13.75" style="3" customWidth="1"/>
     <col min="5" max="5" width="13.5" style="3" customWidth="1"/>
-    <col min="6" max="6" width="57.59765625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="57.625" style="4" customWidth="1"/>
     <col min="7" max="7" width="13.5" style="4" customWidth="1"/>
-    <col min="8" max="8" width="57.59765625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="57.625" style="4" customWidth="1"/>
     <col min="9" max="9" width="21.5" style="4" customWidth="1"/>
-    <col min="10" max="10" width="57.59765625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="19.3984375" style="4" customWidth="1"/>
-    <col min="12" max="12" width="57.69921875" style="4" customWidth="1"/>
-    <col min="13" max="13" width="19.3984375" style="4" customWidth="1"/>
-    <col min="14" max="14" width="57.59765625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="57.625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="19.375" style="4" customWidth="1"/>
+    <col min="12" max="12" width="57.75" style="4" customWidth="1"/>
+    <col min="13" max="13" width="19.375" style="4" customWidth="1"/>
+    <col min="14" max="14" width="57.625" style="4" customWidth="1"/>
     <col min="15" max="15" width="21" style="4" customWidth="1"/>
-    <col min="16" max="16" width="61.59765625" style="4" customWidth="1"/>
+    <col min="16" max="16" width="61.625" style="4" customWidth="1"/>
     <col min="17" max="16384" width="8" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" ht="25.8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" ht="26.25" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
@@ -2173,13 +1878,13 @@
       <c r="O2" s="7"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:16" s="10" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="D3" s="11"/>
       <c r="E3" s="12"/>
       <c r="G3" s="13"/>
     </row>
-    <row r="4" spans="1:16" s="10" customFormat="1" ht="19.8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" s="10" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="14" t="s">
         <v>1</v>
@@ -2190,7 +1895,7 @@
       <c r="F4" s="14"/>
       <c r="G4" s="16"/>
     </row>
-    <row r="5" spans="1:16" s="10" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5" s="17" t="s">
         <v>2</v>
@@ -2201,7 +1906,7 @@
       <c r="F5" s="17"/>
       <c r="G5" s="13"/>
     </row>
-    <row r="6" spans="1:16" s="10" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="B6" s="17" t="s">
         <v>3</v>
@@ -2221,59 +1926,59 @@
       <c r="O6" s="17"/>
       <c r="P6" s="19"/>
     </row>
-    <row r="7" spans="1:16" s="10" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" s="10" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="43" t="s">
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="L7" s="43"/>
-      <c r="M7" s="43"/>
-      <c r="N7" s="43"/>
-      <c r="O7" s="43"/>
-      <c r="P7" s="43"/>
-    </row>
-    <row r="8" spans="1:16" s="10" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+    </row>
+    <row r="8" spans="1:16" s="10" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43" t="s">
+      <c r="F8" s="40"/>
+      <c r="G8" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43" t="s">
+      <c r="H8" s="40"/>
+      <c r="I8" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43" t="s">
+      <c r="J8" s="40"/>
+      <c r="K8" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="L8" s="43"/>
-      <c r="M8" s="43" t="s">
+      <c r="L8" s="40"/>
+      <c r="M8" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="N8" s="43"/>
-      <c r="O8" s="43" t="s">
+      <c r="N8" s="40"/>
+      <c r="O8" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="P8" s="43"/>
-    </row>
-    <row r="9" spans="1:16" s="9" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="P8" s="40"/>
+    </row>
+    <row r="9" spans="1:16" s="9" customFormat="1" ht="34.5" x14ac:dyDescent="0.3">
       <c r="B9" s="34" t="s">
         <v>9</v>
       </c>
@@ -2320,1031 +2025,761 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B10" s="38" t="s">
-        <v>206</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>250</v>
-      </c>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="40"/>
-      <c r="N10" s="40"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="40"/>
-    </row>
-    <row r="11" spans="1:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B11" s="38" t="s">
-        <v>207</v>
-      </c>
-      <c r="C11" s="41" t="s">
-        <v>251</v>
-      </c>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="40"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="40"/>
-      <c r="N11" s="40"/>
-      <c r="O11" s="40"/>
-      <c r="P11" s="40"/>
-    </row>
-    <row r="12" spans="1:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B12" s="38" t="s">
-        <v>208</v>
-      </c>
-      <c r="C12" s="41" t="s">
-        <v>252</v>
-      </c>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="40"/>
-      <c r="M12" s="40"/>
-      <c r="N12" s="40"/>
-      <c r="O12" s="40"/>
-      <c r="P12" s="40"/>
-    </row>
-    <row r="13" spans="1:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B13" s="38" t="s">
-        <v>209</v>
-      </c>
-      <c r="C13" s="41" t="s">
-        <v>253</v>
-      </c>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="40"/>
-      <c r="K13" s="40"/>
-      <c r="L13" s="40"/>
-      <c r="M13" s="40"/>
-      <c r="N13" s="40"/>
-      <c r="O13" s="40"/>
-      <c r="P13" s="40"/>
-    </row>
-    <row r="14" spans="1:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B14" s="38" t="s">
-        <v>210</v>
-      </c>
-      <c r="C14" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="40"/>
-      <c r="M14" s="40"/>
-      <c r="N14" s="40"/>
-      <c r="O14" s="40"/>
-      <c r="P14" s="40"/>
-    </row>
-    <row r="15" spans="1:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B15" s="38" t="s">
-        <v>211</v>
-      </c>
-      <c r="C15" s="41" t="s">
-        <v>255</v>
-      </c>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="40"/>
-      <c r="K15" s="40"/>
-      <c r="L15" s="40"/>
-      <c r="M15" s="40"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="40"/>
-      <c r="P15" s="40"/>
-    </row>
-    <row r="16" spans="1:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B16" s="38" t="s">
-        <v>212</v>
-      </c>
-      <c r="C16" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="40"/>
-      <c r="M16" s="40"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="40"/>
-      <c r="P16" s="40"/>
-    </row>
-    <row r="17" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B17" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="C17" s="41" t="s">
-        <v>257</v>
-      </c>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="40"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="40"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="40"/>
-      <c r="M17" s="40"/>
-      <c r="N17" s="40"/>
-      <c r="O17" s="40"/>
-      <c r="P17" s="40"/>
-    </row>
-    <row r="18" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B18" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="C18" s="41" t="s">
-        <v>258</v>
-      </c>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="40"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="40"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="40"/>
-      <c r="M18" s="40"/>
-      <c r="N18" s="40"/>
-      <c r="O18" s="40"/>
-      <c r="P18" s="40"/>
-    </row>
-    <row r="19" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B19" s="38" t="s">
-        <v>215</v>
-      </c>
-      <c r="C19" s="41" t="s">
-        <v>259</v>
-      </c>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="40"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="40"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="40"/>
-      <c r="M19" s="40"/>
-      <c r="N19" s="40"/>
-      <c r="O19" s="40"/>
-      <c r="P19" s="40"/>
-    </row>
-    <row r="20" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B20" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="C20" s="42" t="s">
-        <v>260</v>
-      </c>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="40"/>
-      <c r="M20" s="40"/>
-      <c r="N20" s="40"/>
-      <c r="O20" s="40"/>
-      <c r="P20" s="40"/>
-    </row>
-    <row r="21" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B21" s="38" t="s">
-        <v>217</v>
-      </c>
-      <c r="C21" s="41" t="s">
-        <v>261</v>
-      </c>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="40"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="40"/>
-      <c r="M21" s="40"/>
-      <c r="N21" s="40"/>
-      <c r="O21" s="40"/>
-      <c r="P21" s="40"/>
-    </row>
-    <row r="22" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B22" s="38" t="s">
-        <v>218</v>
-      </c>
-      <c r="C22" s="41" t="s">
-        <v>262</v>
-      </c>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="40"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="40"/>
-      <c r="M22" s="40"/>
-      <c r="N22" s="40"/>
-      <c r="O22" s="40"/>
-      <c r="P22" s="40"/>
-    </row>
-    <row r="23" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B23" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="C23" s="41" t="s">
-        <v>263</v>
-      </c>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="40"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="40"/>
-      <c r="K23" s="40"/>
-      <c r="L23" s="40"/>
-      <c r="M23" s="40"/>
-      <c r="N23" s="40"/>
-      <c r="O23" s="40"/>
-      <c r="P23" s="40"/>
-    </row>
-    <row r="24" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B24" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="C24" s="41" t="s">
-        <v>264</v>
-      </c>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="40"/>
-      <c r="M24" s="40"/>
-      <c r="N24" s="40"/>
-      <c r="O24" s="40"/>
-      <c r="P24" s="40"/>
-    </row>
-    <row r="25" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B25" s="38" t="s">
-        <v>221</v>
-      </c>
-      <c r="C25" s="41" t="s">
-        <v>265</v>
-      </c>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="40"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="40"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="40"/>
-      <c r="M25" s="40"/>
-      <c r="N25" s="40"/>
-      <c r="O25" s="40"/>
-      <c r="P25" s="40"/>
-    </row>
-    <row r="26" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B26" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="C26" s="41" t="s">
-        <v>266</v>
-      </c>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="40"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="40"/>
-      <c r="M26" s="40"/>
-      <c r="N26" s="40"/>
-      <c r="O26" s="40"/>
-      <c r="P26" s="40"/>
-    </row>
-    <row r="27" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B27" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="C27" s="41" t="s">
-        <v>267</v>
-      </c>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="40"/>
-      <c r="K27" s="40"/>
-      <c r="L27" s="40"/>
-      <c r="M27" s="40"/>
-      <c r="N27" s="40"/>
-      <c r="O27" s="40"/>
-      <c r="P27" s="40"/>
-    </row>
-    <row r="28" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B28" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="C28" s="41" t="s">
-        <v>268</v>
-      </c>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="40"/>
-      <c r="K28" s="40"/>
-      <c r="L28" s="40"/>
-      <c r="M28" s="40"/>
-      <c r="N28" s="40"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="40"/>
-    </row>
-    <row r="29" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B29" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="C29" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="40"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="40"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="40"/>
-      <c r="M29" s="40"/>
-      <c r="N29" s="40"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="40"/>
-    </row>
-    <row r="30" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B30" s="38" t="s">
-        <v>226</v>
-      </c>
-      <c r="C30" s="41" t="s">
-        <v>270</v>
-      </c>
-      <c r="D30" s="39"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="40"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="40"/>
-      <c r="K30" s="40"/>
-      <c r="L30" s="40"/>
-      <c r="M30" s="40"/>
-      <c r="N30" s="40"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="40"/>
-    </row>
-    <row r="31" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B31" s="38" t="s">
-        <v>227</v>
-      </c>
-      <c r="C31" s="41" t="s">
-        <v>271</v>
-      </c>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="40"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="40"/>
-      <c r="K31" s="40"/>
-      <c r="L31" s="40"/>
-      <c r="M31" s="40"/>
-      <c r="N31" s="40"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="40"/>
-    </row>
-    <row r="32" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B32" s="38" t="s">
-        <v>228</v>
-      </c>
-      <c r="C32" s="41" t="s">
-        <v>272</v>
-      </c>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="40"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="40"/>
-      <c r="K32" s="40"/>
-      <c r="L32" s="40"/>
-      <c r="M32" s="40"/>
-      <c r="N32" s="40"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="40"/>
-    </row>
-    <row r="33" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B33" s="38" t="s">
-        <v>229</v>
-      </c>
-      <c r="C33" s="41" t="s">
-        <v>273</v>
-      </c>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="40"/>
-      <c r="H33" s="40"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="40"/>
-      <c r="K33" s="40"/>
-      <c r="L33" s="40"/>
-      <c r="M33" s="40"/>
-      <c r="N33" s="40"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="40"/>
-    </row>
-    <row r="34" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B34" s="38" t="s">
-        <v>230</v>
-      </c>
-      <c r="C34" s="41" t="s">
-        <v>274</v>
-      </c>
-      <c r="D34" s="39"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="40"/>
-      <c r="I34" s="40"/>
-      <c r="J34" s="40"/>
-      <c r="K34" s="40"/>
-      <c r="L34" s="40"/>
-      <c r="M34" s="40"/>
-      <c r="N34" s="40"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="40"/>
-    </row>
-    <row r="35" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B35" s="38" t="s">
-        <v>231</v>
-      </c>
-      <c r="C35" s="41" t="s">
-        <v>275</v>
-      </c>
-      <c r="D35" s="39"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="40"/>
-      <c r="H35" s="40"/>
-      <c r="I35" s="40"/>
-      <c r="J35" s="40"/>
-      <c r="K35" s="40"/>
-      <c r="L35" s="40"/>
-      <c r="M35" s="40"/>
-      <c r="N35" s="40"/>
-      <c r="O35" s="40"/>
-      <c r="P35" s="40"/>
-    </row>
-    <row r="36" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B36" s="38" t="s">
-        <v>232</v>
-      </c>
-      <c r="C36" s="41" t="s">
-        <v>276</v>
-      </c>
-      <c r="D36" s="39"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="40"/>
-      <c r="G36" s="40"/>
-      <c r="H36" s="40"/>
-      <c r="I36" s="40"/>
-      <c r="J36" s="40"/>
-      <c r="K36" s="40"/>
-      <c r="L36" s="40"/>
-      <c r="M36" s="40"/>
-      <c r="N36" s="40"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="40"/>
-    </row>
-    <row r="37" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B37" s="38" t="s">
-        <v>233</v>
-      </c>
-      <c r="C37" s="41" t="s">
-        <v>277</v>
-      </c>
-      <c r="D37" s="39"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="40"/>
-      <c r="H37" s="40"/>
-      <c r="I37" s="40"/>
-      <c r="J37" s="40"/>
-      <c r="K37" s="40"/>
-      <c r="L37" s="40"/>
-      <c r="M37" s="40"/>
-      <c r="N37" s="40"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="40"/>
-    </row>
-    <row r="38" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B38" s="38" t="s">
-        <v>234</v>
-      </c>
-      <c r="C38" s="41" t="s">
-        <v>278</v>
-      </c>
-      <c r="D38" s="39"/>
-      <c r="E38" s="39"/>
-      <c r="F38" s="40"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="40"/>
-      <c r="I38" s="40"/>
-      <c r="J38" s="40"/>
-      <c r="K38" s="40"/>
-      <c r="L38" s="40"/>
-      <c r="M38" s="40"/>
-      <c r="N38" s="40"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="40"/>
-    </row>
-    <row r="39" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B39" s="38" t="s">
-        <v>235</v>
-      </c>
-      <c r="C39" s="41" t="s">
-        <v>279</v>
-      </c>
-      <c r="D39" s="39"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="40"/>
-      <c r="G39" s="40"/>
-      <c r="H39" s="40"/>
-      <c r="I39" s="40"/>
-      <c r="J39" s="40"/>
-      <c r="K39" s="40"/>
-      <c r="L39" s="40"/>
-      <c r="M39" s="40"/>
-      <c r="N39" s="40"/>
-      <c r="O39" s="40"/>
-      <c r="P39" s="40"/>
-    </row>
-    <row r="40" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B40" s="38" t="s">
-        <v>236</v>
-      </c>
-      <c r="C40" s="41" t="s">
-        <v>280</v>
-      </c>
-      <c r="D40" s="39"/>
-      <c r="E40" s="39"/>
-      <c r="F40" s="40"/>
-      <c r="G40" s="40"/>
-      <c r="H40" s="40"/>
-      <c r="I40" s="40"/>
-      <c r="J40" s="40"/>
-      <c r="K40" s="40"/>
-      <c r="L40" s="40"/>
-      <c r="M40" s="40"/>
-      <c r="N40" s="40"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="40"/>
-    </row>
-    <row r="41" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B41" s="38" t="s">
-        <v>237</v>
-      </c>
-      <c r="C41" s="41" t="s">
-        <v>281</v>
-      </c>
-      <c r="D41" s="39"/>
-      <c r="E41" s="39"/>
-      <c r="F41" s="40"/>
-      <c r="G41" s="40"/>
-      <c r="H41" s="40"/>
-      <c r="I41" s="40"/>
-      <c r="J41" s="40"/>
-      <c r="K41" s="40"/>
-      <c r="L41" s="40"/>
-      <c r="M41" s="40"/>
-      <c r="N41" s="40"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="40"/>
-    </row>
-    <row r="42" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B42" s="38" t="s">
-        <v>238</v>
-      </c>
-      <c r="C42" s="41" t="s">
-        <v>282</v>
-      </c>
-      <c r="D42" s="39"/>
-      <c r="E42" s="39"/>
-      <c r="F42" s="40"/>
-      <c r="G42" s="40"/>
-      <c r="H42" s="40"/>
-      <c r="I42" s="40"/>
-      <c r="J42" s="40"/>
-      <c r="K42" s="40"/>
-      <c r="L42" s="40"/>
-      <c r="M42" s="40"/>
-      <c r="N42" s="40"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="40"/>
-    </row>
-    <row r="43" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B43" s="38" t="s">
-        <v>239</v>
-      </c>
-      <c r="C43" s="41" t="s">
-        <v>283</v>
-      </c>
-      <c r="D43" s="39"/>
-      <c r="E43" s="39"/>
-      <c r="F43" s="40"/>
-      <c r="G43" s="40"/>
-      <c r="H43" s="40"/>
-      <c r="I43" s="40"/>
-      <c r="J43" s="40"/>
-      <c r="K43" s="40"/>
-      <c r="L43" s="40"/>
-      <c r="M43" s="40"/>
-      <c r="N43" s="40"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="40"/>
-    </row>
-    <row r="44" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B44" s="38" t="s">
-        <v>240</v>
-      </c>
-      <c r="C44" s="41" t="s">
-        <v>284</v>
-      </c>
-      <c r="D44" s="39"/>
-      <c r="E44" s="39"/>
-      <c r="F44" s="40"/>
-      <c r="G44" s="40"/>
-      <c r="H44" s="40"/>
-      <c r="I44" s="40"/>
-      <c r="J44" s="40"/>
-      <c r="K44" s="40"/>
-      <c r="L44" s="40"/>
-      <c r="M44" s="40"/>
-      <c r="N44" s="40"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="40"/>
-    </row>
-    <row r="45" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B45" s="38" t="s">
-        <v>241</v>
-      </c>
-      <c r="C45" s="41" t="s">
-        <v>285</v>
-      </c>
-      <c r="D45" s="39"/>
-      <c r="E45" s="39"/>
-      <c r="F45" s="40"/>
-      <c r="G45" s="40"/>
-      <c r="H45" s="40"/>
-      <c r="I45" s="40"/>
-      <c r="J45" s="40"/>
-      <c r="K45" s="40"/>
-      <c r="L45" s="40"/>
-      <c r="M45" s="40"/>
-      <c r="N45" s="40"/>
-      <c r="O45" s="40"/>
-      <c r="P45" s="40"/>
-    </row>
-    <row r="46" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B46" s="38" t="s">
-        <v>242</v>
-      </c>
-      <c r="C46" s="41" t="s">
-        <v>286</v>
-      </c>
-      <c r="D46" s="39"/>
-      <c r="E46" s="39"/>
-      <c r="F46" s="40"/>
-      <c r="G46" s="40"/>
-      <c r="H46" s="40"/>
-      <c r="I46" s="40"/>
-      <c r="J46" s="40"/>
-      <c r="K46" s="40"/>
-      <c r="L46" s="40"/>
-      <c r="M46" s="40"/>
-      <c r="N46" s="40"/>
-      <c r="O46" s="40"/>
-      <c r="P46" s="40"/>
-    </row>
-    <row r="47" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B47" s="38" t="s">
-        <v>243</v>
-      </c>
-      <c r="C47" s="41" t="s">
-        <v>287</v>
-      </c>
-      <c r="D47" s="39"/>
-      <c r="E47" s="39"/>
-      <c r="F47" s="40"/>
-      <c r="G47" s="40"/>
-      <c r="H47" s="40"/>
-      <c r="I47" s="40"/>
-      <c r="J47" s="40"/>
-      <c r="K47" s="40"/>
-      <c r="L47" s="40"/>
-      <c r="M47" s="40"/>
-      <c r="N47" s="40"/>
-      <c r="O47" s="40"/>
-      <c r="P47" s="40"/>
-    </row>
-    <row r="48" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B48" s="38" t="s">
-        <v>244</v>
-      </c>
-      <c r="C48" s="41" t="s">
-        <v>288</v>
-      </c>
-      <c r="D48" s="39"/>
-      <c r="E48" s="39"/>
-      <c r="F48" s="40"/>
-      <c r="G48" s="40"/>
-      <c r="H48" s="40"/>
-      <c r="I48" s="40"/>
-      <c r="J48" s="40"/>
-      <c r="K48" s="40"/>
-      <c r="L48" s="40"/>
-      <c r="M48" s="40"/>
-      <c r="N48" s="40"/>
-      <c r="O48" s="40"/>
-      <c r="P48" s="40"/>
-    </row>
-    <row r="49" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B49" s="38" t="s">
-        <v>245</v>
-      </c>
-      <c r="C49" s="41" t="s">
-        <v>289</v>
-      </c>
-      <c r="D49" s="39"/>
-      <c r="E49" s="39"/>
-      <c r="F49" s="40"/>
-      <c r="G49" s="40"/>
-      <c r="H49" s="40"/>
-      <c r="I49" s="40"/>
-      <c r="J49" s="40"/>
-      <c r="K49" s="40"/>
-      <c r="L49" s="40"/>
-      <c r="M49" s="40"/>
-      <c r="N49" s="40"/>
-      <c r="O49" s="40"/>
-      <c r="P49" s="40"/>
-    </row>
-    <row r="50" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B50" s="38" t="s">
-        <v>246</v>
-      </c>
-      <c r="C50" s="41" t="s">
-        <v>290</v>
-      </c>
-      <c r="D50" s="39"/>
-      <c r="E50" s="39"/>
-      <c r="F50" s="40"/>
-      <c r="G50" s="40"/>
-      <c r="H50" s="40"/>
-      <c r="I50" s="40"/>
-      <c r="J50" s="40"/>
-      <c r="K50" s="40"/>
-      <c r="L50" s="40"/>
-      <c r="M50" s="40"/>
-      <c r="N50" s="40"/>
-      <c r="O50" s="40"/>
-      <c r="P50" s="40"/>
-    </row>
-    <row r="51" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B51" s="38" t="s">
-        <v>247</v>
-      </c>
-      <c r="C51" s="41" t="s">
-        <v>291</v>
-      </c>
-      <c r="D51" s="39"/>
-      <c r="E51" s="39"/>
-      <c r="F51" s="40"/>
-      <c r="G51" s="40"/>
-      <c r="H51" s="40"/>
-      <c r="I51" s="40"/>
-      <c r="J51" s="40"/>
-      <c r="K51" s="40"/>
-      <c r="L51" s="40"/>
-      <c r="M51" s="40"/>
-      <c r="N51" s="40"/>
-      <c r="O51" s="40"/>
-      <c r="P51" s="40"/>
-    </row>
-    <row r="52" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B52" s="38" t="s">
-        <v>248</v>
-      </c>
-      <c r="C52" s="41" t="s">
-        <v>292</v>
-      </c>
-      <c r="D52" s="39"/>
-      <c r="E52" s="39"/>
-      <c r="F52" s="40"/>
-      <c r="G52" s="40"/>
-      <c r="H52" s="40"/>
-      <c r="I52" s="40"/>
-      <c r="J52" s="40"/>
-      <c r="K52" s="40"/>
-      <c r="L52" s="40"/>
-      <c r="M52" s="40"/>
-      <c r="N52" s="40"/>
-      <c r="O52" s="40"/>
-      <c r="P52" s="40"/>
-    </row>
-    <row r="53" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B53" s="38" t="s">
-        <v>249</v>
-      </c>
-      <c r="C53" s="41" t="s">
-        <v>293</v>
-      </c>
-      <c r="D53" s="39"/>
-      <c r="E53" s="39"/>
-      <c r="F53" s="40"/>
-      <c r="G53" s="40"/>
-      <c r="H53" s="40"/>
-      <c r="I53" s="40"/>
-      <c r="J53" s="40"/>
-      <c r="K53" s="40"/>
-      <c r="L53" s="40"/>
-      <c r="M53" s="40"/>
-      <c r="N53" s="40"/>
-      <c r="O53" s="40"/>
-      <c r="P53" s="40"/>
-    </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B54" s="40"/>
-      <c r="C54" s="40"/>
-      <c r="D54" s="39"/>
-      <c r="E54" s="39"/>
-      <c r="F54" s="40"/>
-      <c r="G54" s="40"/>
-      <c r="H54" s="40"/>
-      <c r="I54" s="40"/>
-      <c r="J54" s="40"/>
-      <c r="K54" s="40"/>
-      <c r="L54" s="40"/>
-      <c r="M54" s="40"/>
-      <c r="N54" s="40"/>
-      <c r="O54" s="40"/>
-      <c r="P54" s="40"/>
-    </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B55" s="40"/>
-      <c r="C55" s="40"/>
-      <c r="D55" s="39"/>
-      <c r="E55" s="39"/>
-      <c r="F55" s="40"/>
-      <c r="G55" s="40"/>
-      <c r="H55" s="40"/>
-      <c r="I55" s="40"/>
-      <c r="J55" s="40"/>
-      <c r="K55" s="40"/>
-      <c r="L55" s="40"/>
-      <c r="M55" s="40"/>
-      <c r="N55" s="40"/>
-      <c r="O55" s="40"/>
-      <c r="P55" s="40"/>
-    </row>
-    <row r="56" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B56" s="40"/>
-      <c r="C56" s="40"/>
-      <c r="D56" s="39"/>
-      <c r="E56" s="39"/>
-      <c r="F56" s="40"/>
-      <c r="G56" s="40"/>
-      <c r="H56" s="40"/>
-      <c r="I56" s="40"/>
-      <c r="J56" s="40"/>
-      <c r="K56" s="40"/>
-      <c r="L56" s="40"/>
-      <c r="M56" s="40"/>
-      <c r="N56" s="40"/>
-      <c r="O56" s="40"/>
-      <c r="P56" s="40"/>
-    </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B57" s="40"/>
-      <c r="C57" s="40"/>
-      <c r="D57" s="39"/>
-      <c r="E57" s="39"/>
-      <c r="F57" s="40"/>
-      <c r="G57" s="40"/>
-      <c r="H57" s="40"/>
-      <c r="I57" s="40"/>
-      <c r="J57" s="40"/>
-      <c r="K57" s="40"/>
-      <c r="L57" s="40"/>
-      <c r="M57" s="40"/>
-      <c r="N57" s="40"/>
-      <c r="O57" s="40"/>
-      <c r="P57" s="40"/>
-    </row>
-    <row r="58" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B58" s="40"/>
-      <c r="C58" s="40"/>
-      <c r="D58" s="39"/>
-      <c r="E58" s="39"/>
-      <c r="F58" s="40"/>
-      <c r="G58" s="40"/>
-      <c r="H58" s="40"/>
-      <c r="I58" s="40"/>
-      <c r="J58" s="40"/>
-      <c r="K58" s="40"/>
-      <c r="L58" s="40"/>
-      <c r="M58" s="40"/>
-      <c r="N58" s="40"/>
-      <c r="O58" s="40"/>
-      <c r="P58" s="40"/>
-    </row>
-    <row r="59" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B59" s="40"/>
-      <c r="C59" s="40"/>
-      <c r="D59" s="39"/>
-      <c r="E59" s="39"/>
-      <c r="F59" s="40"/>
-      <c r="G59" s="40"/>
-      <c r="H59" s="40"/>
-      <c r="I59" s="40"/>
-      <c r="J59" s="40"/>
-      <c r="K59" s="40"/>
-      <c r="L59" s="40"/>
-      <c r="M59" s="40"/>
-      <c r="N59" s="40"/>
-      <c r="O59" s="40"/>
-      <c r="P59" s="40"/>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B10" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="39"/>
+      <c r="N10" s="39"/>
+      <c r="O10" s="39"/>
+      <c r="P10" s="39"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B11" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="39"/>
+      <c r="N11" s="39"/>
+      <c r="O11" s="39"/>
+      <c r="P11" s="39"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B12" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="39"/>
+      <c r="M12" s="39"/>
+      <c r="N12" s="39"/>
+      <c r="O12" s="39"/>
+      <c r="P12" s="39"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B13" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="39"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="39"/>
+      <c r="N13" s="39"/>
+      <c r="O13" s="39"/>
+      <c r="P13" s="39"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B14" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="39"/>
+      <c r="N14" s="39"/>
+      <c r="O14" s="39"/>
+      <c r="P14" s="39"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B15" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="39"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="39"/>
+      <c r="P15" s="39"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B16" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="39"/>
+      <c r="M16" s="39"/>
+      <c r="N16" s="39"/>
+      <c r="O16" s="39"/>
+      <c r="P16" s="39"/>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B17" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="39"/>
+      <c r="M17" s="39"/>
+      <c r="N17" s="39"/>
+      <c r="O17" s="39"/>
+      <c r="P17" s="39"/>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B18" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="39"/>
+      <c r="M18" s="39"/>
+      <c r="N18" s="39"/>
+      <c r="O18" s="39"/>
+      <c r="P18" s="39"/>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B19" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="39"/>
+      <c r="M19" s="39"/>
+      <c r="N19" s="39"/>
+      <c r="O19" s="39"/>
+      <c r="P19" s="39"/>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B20" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="39"/>
+      <c r="O20" s="39"/>
+      <c r="P20" s="39"/>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B21" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="39"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="39"/>
+      <c r="P21" s="39"/>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B22" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="39"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="39"/>
+      <c r="O22" s="39"/>
+      <c r="P22" s="39"/>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B23" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="39"/>
+      <c r="P23" s="39"/>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B24" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="39"/>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B25" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="39"/>
+      <c r="N25" s="39"/>
+      <c r="O25" s="39"/>
+      <c r="P25" s="39"/>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B26" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
+      <c r="K26" s="39"/>
+      <c r="L26" s="39"/>
+      <c r="M26" s="39"/>
+      <c r="N26" s="39"/>
+      <c r="O26" s="39"/>
+      <c r="P26" s="39"/>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B27" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="39"/>
+      <c r="K27" s="39"/>
+      <c r="L27" s="39"/>
+      <c r="M27" s="39"/>
+      <c r="N27" s="39"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="39"/>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B28" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="39"/>
+      <c r="K28" s="39"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="39"/>
+      <c r="N28" s="39"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="39"/>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B29" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="39"/>
+      <c r="K29" s="39"/>
+      <c r="L29" s="39"/>
+      <c r="M29" s="39"/>
+      <c r="N29" s="39"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="39"/>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B30" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="39"/>
+      <c r="K30" s="39"/>
+      <c r="L30" s="39"/>
+      <c r="M30" s="39"/>
+      <c r="N30" s="39"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="39"/>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B31" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="39"/>
+      <c r="K31" s="39"/>
+      <c r="L31" s="39"/>
+      <c r="M31" s="39"/>
+      <c r="N31" s="39"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="39"/>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B32" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="39"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="39"/>
+      <c r="K32" s="39"/>
+      <c r="L32" s="39"/>
+      <c r="M32" s="39"/>
+      <c r="N32" s="39"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="39"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B33" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="39"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="39"/>
+      <c r="K33" s="39"/>
+      <c r="L33" s="39"/>
+      <c r="M33" s="39"/>
+      <c r="N33" s="39"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="39"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B34" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="D34" s="38"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="39"/>
+      <c r="J34" s="39"/>
+      <c r="K34" s="39"/>
+      <c r="L34" s="39"/>
+      <c r="M34" s="39"/>
+      <c r="N34" s="39"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="39"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B35" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="39"/>
+      <c r="I35" s="39"/>
+      <c r="J35" s="39"/>
+      <c r="K35" s="39"/>
+      <c r="L35" s="39"/>
+      <c r="M35" s="39"/>
+      <c r="N35" s="39"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="39"/>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B36" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="39"/>
+      <c r="J36" s="39"/>
+      <c r="K36" s="39"/>
+      <c r="L36" s="39"/>
+      <c r="M36" s="39"/>
+      <c r="N36" s="39"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="39"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B37" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="D37" s="38"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="39"/>
+      <c r="H37" s="39"/>
+      <c r="I37" s="39"/>
+      <c r="J37" s="39"/>
+      <c r="K37" s="39"/>
+      <c r="L37" s="39"/>
+      <c r="M37" s="39"/>
+      <c r="N37" s="39"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="39"/>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B38" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="D38" s="38"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="39"/>
+      <c r="I38" s="39"/>
+      <c r="J38" s="39"/>
+      <c r="K38" s="39"/>
+      <c r="L38" s="39"/>
+      <c r="M38" s="39"/>
+      <c r="N38" s="39"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="39"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B39" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C39" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="D39" s="38"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="39"/>
+      <c r="H39" s="39"/>
+      <c r="I39" s="39"/>
+      <c r="J39" s="39"/>
+      <c r="K39" s="39"/>
+      <c r="L39" s="39"/>
+      <c r="M39" s="39"/>
+      <c r="N39" s="39"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="39"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B40" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C40" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="D40" s="38"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="39"/>
+      <c r="G40" s="39"/>
+      <c r="H40" s="39"/>
+      <c r="I40" s="39"/>
+      <c r="J40" s="39"/>
+      <c r="K40" s="39"/>
+      <c r="L40" s="39"/>
+      <c r="M40" s="39"/>
+      <c r="N40" s="39"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="39"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B41" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="D41" s="38"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="39"/>
+      <c r="G41" s="39"/>
+      <c r="H41" s="39"/>
+      <c r="I41" s="39"/>
+      <c r="J41" s="39"/>
+      <c r="K41" s="39"/>
+      <c r="L41" s="39"/>
+      <c r="M41" s="39"/>
+      <c r="N41" s="39"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="39"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B42" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="D42" s="38"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="39"/>
+      <c r="G42" s="39"/>
+      <c r="H42" s="39"/>
+      <c r="I42" s="39"/>
+      <c r="J42" s="39"/>
+      <c r="K42" s="39"/>
+      <c r="L42" s="39"/>
+      <c r="M42" s="39"/>
+      <c r="N42" s="39"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="39"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B43" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="D43" s="38"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="39"/>
+      <c r="G43" s="39"/>
+      <c r="H43" s="39"/>
+      <c r="I43" s="39"/>
+      <c r="J43" s="39"/>
+      <c r="K43" s="39"/>
+      <c r="L43" s="39"/>
+      <c r="M43" s="39"/>
+      <c r="N43" s="39"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="39"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B44" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="D44" s="38"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="39"/>
+      <c r="G44" s="39"/>
+      <c r="H44" s="39"/>
+      <c r="I44" s="39"/>
+      <c r="J44" s="39"/>
+      <c r="K44" s="39"/>
+      <c r="L44" s="39"/>
+      <c r="M44" s="39"/>
+      <c r="N44" s="39"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="39"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B45" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="D45" s="38"/>
+      <c r="E45" s="38"/>
+      <c r="F45" s="39"/>
+      <c r="G45" s="39"/>
+      <c r="H45" s="39"/>
+      <c r="I45" s="39"/>
+      <c r="J45" s="39"/>
+      <c r="K45" s="39"/>
+      <c r="L45" s="39"/>
+      <c r="M45" s="39"/>
+      <c r="N45" s="39"/>
+      <c r="O45" s="39"/>
+      <c r="P45" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3370,33 +2805,33 @@
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:P101"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="14.4" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.19921875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.69921875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="3.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.75" style="4" customWidth="1"/>
     <col min="3" max="3" width="34.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.69921875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="13.75" style="3" customWidth="1"/>
     <col min="5" max="5" width="13.5" style="3" customWidth="1"/>
-    <col min="6" max="6" width="57.59765625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="57.625" style="4" customWidth="1"/>
     <col min="7" max="7" width="13.5" style="4" customWidth="1"/>
-    <col min="8" max="8" width="57.59765625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="57.625" style="4" customWidth="1"/>
     <col min="9" max="9" width="21.5" style="4" customWidth="1"/>
-    <col min="10" max="10" width="57.59765625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="19.3984375" style="4" customWidth="1"/>
-    <col min="12" max="12" width="57.69921875" style="4" customWidth="1"/>
-    <col min="13" max="13" width="19.3984375" style="4" customWidth="1"/>
-    <col min="14" max="14" width="57.59765625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="57.625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="19.375" style="4" customWidth="1"/>
+    <col min="12" max="12" width="57.75" style="4" customWidth="1"/>
+    <col min="13" max="13" width="19.375" style="4" customWidth="1"/>
+    <col min="14" max="14" width="57.625" style="4" customWidth="1"/>
     <col min="15" max="15" width="21" style="4" customWidth="1"/>
-    <col min="16" max="16" width="61.59765625" style="4" customWidth="1"/>
+    <col min="16" max="16" width="61.625" style="4" customWidth="1"/>
     <col min="17" max="16384" width="8" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" ht="25.8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" ht="26.25" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
@@ -3415,13 +2850,13 @@
       <c r="O2" s="7"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:16" s="10" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="D3" s="11"/>
       <c r="E3" s="12"/>
       <c r="G3" s="13"/>
     </row>
-    <row r="4" spans="1:16" s="10" customFormat="1" ht="19.8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" s="10" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="14" t="s">
         <v>1</v>
@@ -3432,7 +2867,7 @@
       <c r="F4" s="14"/>
       <c r="G4" s="16"/>
     </row>
-    <row r="5" spans="1:16" s="10" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5" s="17" t="s">
         <v>2</v>
@@ -3443,7 +2878,7 @@
       <c r="F5" s="17"/>
       <c r="G5" s="13"/>
     </row>
-    <row r="6" spans="1:16" s="10" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="B6" s="17" t="s">
         <v>3</v>
@@ -3463,59 +2898,59 @@
       <c r="O6" s="17"/>
       <c r="P6" s="19"/>
     </row>
-    <row r="7" spans="1:16" s="10" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" s="10" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="43" t="s">
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="L7" s="43"/>
-      <c r="M7" s="43"/>
-      <c r="N7" s="43"/>
-      <c r="O7" s="43"/>
-      <c r="P7" s="43"/>
-    </row>
-    <row r="8" spans="1:16" s="10" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+    </row>
+    <row r="8" spans="1:16" s="10" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43" t="s">
+      <c r="F8" s="40"/>
+      <c r="G8" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43" t="s">
+      <c r="H8" s="40"/>
+      <c r="I8" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43" t="s">
+      <c r="J8" s="40"/>
+      <c r="K8" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="L8" s="43"/>
-      <c r="M8" s="43" t="s">
+      <c r="L8" s="40"/>
+      <c r="M8" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="N8" s="43"/>
-      <c r="O8" s="43" t="s">
+      <c r="N8" s="40"/>
+      <c r="O8" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="P8" s="43"/>
-    </row>
-    <row r="9" spans="1:16" s="9" customFormat="1" ht="35.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="P8" s="40"/>
+    </row>
+    <row r="9" spans="1:16" s="9" customFormat="1" ht="35.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="20" t="s">
         <v>9</v>
       </c>
@@ -3562,7 +2997,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B10" s="24" t="s">
         <v>13</v>
       </c>
@@ -3597,7 +3032,7 @@
       <c r="O10" s="26"/>
       <c r="P10" s="27"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B11" s="24" t="s">
         <v>20</v>
       </c>
@@ -3618,7 +3053,7 @@
       <c r="O11" s="25"/>
       <c r="P11" s="25"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B12" s="24" t="s">
         <v>21</v>
       </c>
@@ -3639,7 +3074,7 @@
       <c r="O12" s="25"/>
       <c r="P12" s="25"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B13" s="24" t="s">
         <v>22</v>
       </c>
@@ -3660,7 +3095,7 @@
       <c r="O13" s="25"/>
       <c r="P13" s="25"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B14" s="24" t="s">
         <v>23</v>
       </c>
@@ -3681,7 +3116,7 @@
       <c r="O14" s="25"/>
       <c r="P14" s="25"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B15" s="24" t="s">
         <v>24</v>
       </c>
@@ -3702,7 +3137,7 @@
       <c r="O15" s="25"/>
       <c r="P15" s="25"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B16" s="24" t="s">
         <v>25</v>
       </c>
@@ -3723,7 +3158,7 @@
       <c r="O16" s="25"/>
       <c r="P16" s="25"/>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B17" s="24" t="s">
         <v>26</v>
       </c>
@@ -3744,7 +3179,7 @@
       <c r="O17" s="25"/>
       <c r="P17" s="25"/>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B18" s="24" t="s">
         <v>27</v>
       </c>
@@ -3765,7 +3200,7 @@
       <c r="O18" s="25"/>
       <c r="P18" s="25"/>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" s="24" t="s">
         <v>28</v>
       </c>
@@ -3786,7 +3221,7 @@
       <c r="O19" s="25"/>
       <c r="P19" s="25"/>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B20" s="24" t="s">
         <v>29</v>
       </c>
@@ -3807,7 +3242,7 @@
       <c r="O20" s="25"/>
       <c r="P20" s="25"/>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B21" s="24" t="s">
         <v>30</v>
       </c>
@@ -3828,7 +3263,7 @@
       <c r="O21" s="25"/>
       <c r="P21" s="25"/>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B22" s="24" t="s">
         <v>31</v>
       </c>
@@ -3849,7 +3284,7 @@
       <c r="O22" s="25"/>
       <c r="P22" s="25"/>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B23" s="24" t="s">
         <v>32</v>
       </c>
@@ -3870,7 +3305,7 @@
       <c r="O23" s="25"/>
       <c r="P23" s="25"/>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B24" s="24" t="s">
         <v>33</v>
       </c>
@@ -3891,7 +3326,7 @@
       <c r="O24" s="25"/>
       <c r="P24" s="25"/>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B25" s="24" t="s">
         <v>34</v>
       </c>
@@ -3912,7 +3347,7 @@
       <c r="O25" s="25"/>
       <c r="P25" s="25"/>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B26" s="24" t="s">
         <v>35</v>
       </c>
@@ -3933,7 +3368,7 @@
       <c r="O26" s="25"/>
       <c r="P26" s="25"/>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B27" s="24" t="s">
         <v>36</v>
       </c>
@@ -3954,7 +3389,7 @@
       <c r="O27" s="25"/>
       <c r="P27" s="25"/>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B28" s="24" t="s">
         <v>37</v>
       </c>
@@ -3975,7 +3410,7 @@
       <c r="O28" s="25"/>
       <c r="P28" s="25"/>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B29" s="24" t="s">
         <v>38</v>
       </c>
@@ -3996,7 +3431,7 @@
       <c r="O29" s="25"/>
       <c r="P29" s="25"/>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B30" s="24" t="s">
         <v>39</v>
       </c>
@@ -4017,7 +3452,7 @@
       <c r="O30" s="25"/>
       <c r="P30" s="25"/>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B31" s="24" t="s">
         <v>40</v>
       </c>
@@ -4038,7 +3473,7 @@
       <c r="O31" s="25"/>
       <c r="P31" s="25"/>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" s="24" t="s">
         <v>41</v>
       </c>
@@ -4059,7 +3494,7 @@
       <c r="O32" s="25"/>
       <c r="P32" s="25"/>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B33" s="24" t="s">
         <v>42</v>
       </c>
@@ -4080,7 +3515,7 @@
       <c r="O33" s="25"/>
       <c r="P33" s="25"/>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B34" s="24" t="s">
         <v>43</v>
       </c>
@@ -4101,7 +3536,7 @@
       <c r="O34" s="25"/>
       <c r="P34" s="25"/>
     </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B35" s="24" t="s">
         <v>44</v>
       </c>
@@ -4122,7 +3557,7 @@
       <c r="O35" s="25"/>
       <c r="P35" s="25"/>
     </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B36" s="24" t="s">
         <v>45</v>
       </c>
@@ -4143,7 +3578,7 @@
       <c r="O36" s="25"/>
       <c r="P36" s="25"/>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B37" s="24" t="s">
         <v>46</v>
       </c>
@@ -4164,7 +3599,7 @@
       <c r="O37" s="25"/>
       <c r="P37" s="25"/>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B38" s="24" t="s">
         <v>47</v>
       </c>
@@ -4185,7 +3620,7 @@
       <c r="O38" s="25"/>
       <c r="P38" s="25"/>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B39" s="24" t="s">
         <v>48</v>
       </c>
@@ -4206,7 +3641,7 @@
       <c r="O39" s="25"/>
       <c r="P39" s="25"/>
     </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B40" s="24" t="s">
         <v>49</v>
       </c>
@@ -4227,7 +3662,7 @@
       <c r="O40" s="25"/>
       <c r="P40" s="25"/>
     </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B41" s="24" t="s">
         <v>50</v>
       </c>
@@ -4248,7 +3683,7 @@
       <c r="O41" s="25"/>
       <c r="P41" s="25"/>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B42" s="24" t="s">
         <v>51</v>
       </c>
@@ -4269,7 +3704,7 @@
       <c r="O42" s="25"/>
       <c r="P42" s="25"/>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B43" s="24" t="s">
         <v>52</v>
       </c>
@@ -4290,7 +3725,7 @@
       <c r="O43" s="25"/>
       <c r="P43" s="25"/>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B44" s="24" t="s">
         <v>53</v>
       </c>
@@ -4311,7 +3746,7 @@
       <c r="O44" s="25"/>
       <c r="P44" s="25"/>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B45" s="24" t="s">
         <v>54</v>
       </c>
@@ -4332,7 +3767,7 @@
       <c r="O45" s="25"/>
       <c r="P45" s="25"/>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B46" s="24" t="s">
         <v>55</v>
       </c>
@@ -4353,7 +3788,7 @@
       <c r="O46" s="25"/>
       <c r="P46" s="25"/>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B47" s="24" t="s">
         <v>56</v>
       </c>
@@ -4374,7 +3809,7 @@
       <c r="O47" s="25"/>
       <c r="P47" s="25"/>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B48" s="24" t="s">
         <v>57</v>
       </c>
@@ -4395,7 +3830,7 @@
       <c r="O48" s="25"/>
       <c r="P48" s="25"/>
     </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B49" s="24" t="s">
         <v>58</v>
       </c>
@@ -4416,7 +3851,7 @@
       <c r="O49" s="25"/>
       <c r="P49" s="25"/>
     </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B50" s="24" t="s">
         <v>59</v>
       </c>
@@ -4437,7 +3872,7 @@
       <c r="O50" s="25"/>
       <c r="P50" s="25"/>
     </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B51" s="24" t="s">
         <v>60</v>
       </c>
@@ -4458,7 +3893,7 @@
       <c r="O51" s="25"/>
       <c r="P51" s="25"/>
     </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B52" s="24" t="s">
         <v>61</v>
       </c>
@@ -4479,7 +3914,7 @@
       <c r="O52" s="25"/>
       <c r="P52" s="25"/>
     </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B53" s="24" t="s">
         <v>62</v>
       </c>
@@ -4500,7 +3935,7 @@
       <c r="O53" s="25"/>
       <c r="P53" s="25"/>
     </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B54" s="24" t="s">
         <v>63</v>
       </c>
@@ -4521,7 +3956,7 @@
       <c r="O54" s="25"/>
       <c r="P54" s="25"/>
     </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B55" s="24" t="s">
         <v>64</v>
       </c>
@@ -4542,7 +3977,7 @@
       <c r="O55" s="25"/>
       <c r="P55" s="25"/>
     </row>
-    <row r="56" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B56" s="24" t="s">
         <v>65</v>
       </c>
@@ -4563,7 +3998,7 @@
       <c r="O56" s="25"/>
       <c r="P56" s="25"/>
     </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B57" s="24" t="s">
         <v>66</v>
       </c>
@@ -4584,7 +4019,7 @@
       <c r="O57" s="25"/>
       <c r="P57" s="25"/>
     </row>
-    <row r="58" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B58" s="24" t="s">
         <v>67</v>
       </c>
@@ -4605,7 +4040,7 @@
       <c r="O58" s="25"/>
       <c r="P58" s="25"/>
     </row>
-    <row r="59" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="59" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B59" s="24" t="s">
         <v>68</v>
       </c>
@@ -4626,7 +4061,7 @@
       <c r="O59" s="25"/>
       <c r="P59" s="25"/>
     </row>
-    <row r="60" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B60" s="24" t="s">
         <v>69</v>
       </c>
@@ -4647,7 +4082,7 @@
       <c r="O60" s="25"/>
       <c r="P60" s="25"/>
     </row>
-    <row r="61" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="61" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B61" s="24" t="s">
         <v>70</v>
       </c>
@@ -4668,7 +4103,7 @@
       <c r="O61" s="25"/>
       <c r="P61" s="25"/>
     </row>
-    <row r="62" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="62" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B62" s="24" t="s">
         <v>71</v>
       </c>
@@ -4689,7 +4124,7 @@
       <c r="O62" s="25"/>
       <c r="P62" s="25"/>
     </row>
-    <row r="63" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B63" s="24" t="s">
         <v>72</v>
       </c>
@@ -4710,7 +4145,7 @@
       <c r="O63" s="25"/>
       <c r="P63" s="25"/>
     </row>
-    <row r="64" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="64" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B64" s="24" t="s">
         <v>73</v>
       </c>
@@ -4731,7 +4166,7 @@
       <c r="O64" s="25"/>
       <c r="P64" s="25"/>
     </row>
-    <row r="65" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="65" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B65" s="24" t="s">
         <v>74</v>
       </c>
@@ -4752,7 +4187,7 @@
       <c r="O65" s="25"/>
       <c r="P65" s="25"/>
     </row>
-    <row r="66" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="66" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B66" s="24" t="s">
         <v>75</v>
       </c>
@@ -4773,7 +4208,7 @@
       <c r="O66" s="25"/>
       <c r="P66" s="25"/>
     </row>
-    <row r="67" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="67" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B67" s="24" t="s">
         <v>76</v>
       </c>
@@ -4794,7 +4229,7 @@
       <c r="O67" s="25"/>
       <c r="P67" s="25"/>
     </row>
-    <row r="68" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="68" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B68" s="24" t="s">
         <v>77</v>
       </c>
@@ -4815,7 +4250,7 @@
       <c r="O68" s="25"/>
       <c r="P68" s="25"/>
     </row>
-    <row r="69" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="69" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B69" s="24" t="s">
         <v>78</v>
       </c>
@@ -4836,7 +4271,7 @@
       <c r="O69" s="25"/>
       <c r="P69" s="25"/>
     </row>
-    <row r="70" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="70" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B70" s="24" t="s">
         <v>79</v>
       </c>
@@ -4857,7 +4292,7 @@
       <c r="O70" s="25"/>
       <c r="P70" s="25"/>
     </row>
-    <row r="71" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="71" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B71" s="24" t="s">
         <v>80</v>
       </c>
@@ -4878,7 +4313,7 @@
       <c r="O71" s="25"/>
       <c r="P71" s="25"/>
     </row>
-    <row r="72" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="72" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B72" s="24" t="s">
         <v>81</v>
       </c>
@@ -4899,7 +4334,7 @@
       <c r="O72" s="25"/>
       <c r="P72" s="25"/>
     </row>
-    <row r="73" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="73" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B73" s="24" t="s">
         <v>82</v>
       </c>
@@ -4920,7 +4355,7 @@
       <c r="O73" s="25"/>
       <c r="P73" s="25"/>
     </row>
-    <row r="74" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="74" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B74" s="24" t="s">
         <v>83</v>
       </c>
@@ -4941,7 +4376,7 @@
       <c r="O74" s="25"/>
       <c r="P74" s="25"/>
     </row>
-    <row r="75" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="75" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B75" s="24" t="s">
         <v>84</v>
       </c>
@@ -4962,7 +4397,7 @@
       <c r="O75" s="25"/>
       <c r="P75" s="25"/>
     </row>
-    <row r="76" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="76" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B76" s="24" t="s">
         <v>85</v>
       </c>
@@ -4983,7 +4418,7 @@
       <c r="O76" s="25"/>
       <c r="P76" s="25"/>
     </row>
-    <row r="77" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="77" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B77" s="24" t="s">
         <v>86</v>
       </c>
@@ -5004,7 +4439,7 @@
       <c r="O77" s="25"/>
       <c r="P77" s="25"/>
     </row>
-    <row r="78" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="78" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B78" s="24" t="s">
         <v>87</v>
       </c>
@@ -5025,7 +4460,7 @@
       <c r="O78" s="25"/>
       <c r="P78" s="25"/>
     </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="79" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B79" s="24" t="s">
         <v>88</v>
       </c>
@@ -5046,7 +4481,7 @@
       <c r="O79" s="25"/>
       <c r="P79" s="25"/>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B80" s="24" t="s">
         <v>89</v>
       </c>
@@ -5067,7 +4502,7 @@
       <c r="O80" s="25"/>
       <c r="P80" s="25"/>
     </row>
-    <row r="81" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="81" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B81" s="24" t="s">
         <v>90</v>
       </c>
@@ -5088,7 +4523,7 @@
       <c r="O81" s="25"/>
       <c r="P81" s="25"/>
     </row>
-    <row r="82" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="82" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B82" s="24" t="s">
         <v>91</v>
       </c>
@@ -5109,7 +4544,7 @@
       <c r="O82" s="25"/>
       <c r="P82" s="25"/>
     </row>
-    <row r="83" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B83" s="24" t="s">
         <v>92</v>
       </c>
@@ -5130,7 +4565,7 @@
       <c r="O83" s="25"/>
       <c r="P83" s="25"/>
     </row>
-    <row r="84" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="84" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B84" s="24" t="s">
         <v>93</v>
       </c>
@@ -5151,7 +4586,7 @@
       <c r="O84" s="25"/>
       <c r="P84" s="25"/>
     </row>
-    <row r="85" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B85" s="24" t="s">
         <v>94</v>
       </c>
@@ -5172,7 +4607,7 @@
       <c r="O85" s="25"/>
       <c r="P85" s="25"/>
     </row>
-    <row r="86" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="86" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B86" s="24" t="s">
         <v>95</v>
       </c>
@@ -5193,7 +4628,7 @@
       <c r="O86" s="25"/>
       <c r="P86" s="25"/>
     </row>
-    <row r="87" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="87" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B87" s="24" t="s">
         <v>96</v>
       </c>
@@ -5214,7 +4649,7 @@
       <c r="O87" s="25"/>
       <c r="P87" s="25"/>
     </row>
-    <row r="88" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="88" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B88" s="24" t="s">
         <v>97</v>
       </c>
@@ -5235,7 +4670,7 @@
       <c r="O88" s="25"/>
       <c r="P88" s="25"/>
     </row>
-    <row r="89" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="89" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B89" s="24" t="s">
         <v>98</v>
       </c>
@@ -5256,7 +4691,7 @@
       <c r="O89" s="25"/>
       <c r="P89" s="25"/>
     </row>
-    <row r="90" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="90" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B90" s="24" t="s">
         <v>99</v>
       </c>
@@ -5277,7 +4712,7 @@
       <c r="O90" s="25"/>
       <c r="P90" s="25"/>
     </row>
-    <row r="91" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="91" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B91" s="24" t="s">
         <v>100</v>
       </c>
@@ -5298,7 +4733,7 @@
       <c r="O91" s="25"/>
       <c r="P91" s="25"/>
     </row>
-    <row r="92" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="92" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B92" s="24" t="s">
         <v>101</v>
       </c>
@@ -5319,7 +4754,7 @@
       <c r="O92" s="25"/>
       <c r="P92" s="25"/>
     </row>
-    <row r="93" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="93" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B93" s="24" t="s">
         <v>102</v>
       </c>
@@ -5340,7 +4775,7 @@
       <c r="O93" s="25"/>
       <c r="P93" s="25"/>
     </row>
-    <row r="94" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="94" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B94" s="24" t="s">
         <v>103</v>
       </c>
@@ -5361,7 +4796,7 @@
       <c r="O94" s="25"/>
       <c r="P94" s="25"/>
     </row>
-    <row r="95" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="95" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B95" s="24" t="s">
         <v>104</v>
       </c>
@@ -5382,7 +4817,7 @@
       <c r="O95" s="25"/>
       <c r="P95" s="25"/>
     </row>
-    <row r="96" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="96" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B96" s="24" t="s">
         <v>105</v>
       </c>
@@ -5403,7 +4838,7 @@
       <c r="O96" s="25"/>
       <c r="P96" s="25"/>
     </row>
-    <row r="97" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="97" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B97" s="24" t="s">
         <v>106</v>
       </c>
@@ -5424,7 +4859,7 @@
       <c r="O97" s="25"/>
       <c r="P97" s="25"/>
     </row>
-    <row r="98" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="98" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B98" s="24" t="s">
         <v>107</v>
       </c>
@@ -5445,7 +4880,7 @@
       <c r="O98" s="25"/>
       <c r="P98" s="25"/>
     </row>
-    <row r="99" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="99" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B99" s="24" t="s">
         <v>108</v>
       </c>
@@ -5466,7 +4901,7 @@
       <c r="O99" s="25"/>
       <c r="P99" s="25"/>
     </row>
-    <row r="100" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="100" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B100" s="24" t="s">
         <v>109</v>
       </c>
@@ -5487,7 +4922,7 @@
       <c r="O100" s="25"/>
       <c r="P100" s="25"/>
     </row>
-    <row r="101" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="101" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B101" s="29" t="s">
         <v>110</v>
       </c>

--- a/upload_excel/KV_Test.xlsx
+++ b/upload_excel/KV_Test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyuns\Downloads\unpacktool\unpacktool\upload_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1323619-D61A-44D8-9AE5-588E200C9AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{350821ED-4037-4A8F-959B-A46F84B6ED58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{D524A933-36B5-41C2-8BA2-68E0D1C505E5}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'20230117 AA - Livestream'!$B$9:$P$96</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TEST!$B$9:$P$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TEST!$B$9:$M$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -187,7 +187,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="209">
   <si>
     <r>
       <t>[</t>
@@ -954,12 +954,24 @@
     <t>an-la</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
+  <si>
+    <t>an-ac</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>hd08-hero-kv</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>co76-feature-kv</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1101,6 +1113,13 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1122,7 +1141,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1282,12 +1301,40 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1299,7 +1346,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1411,9 +1458,6 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1421,6 +1465,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1832,7 +1888,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P45"/>
+  <dimension ref="A1:V45"/>
   <sheetFormatPr defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.25" style="1" customWidth="1"/>
@@ -1840,26 +1896,29 @@
     <col min="3" max="3" width="33.375" style="4" customWidth="1"/>
     <col min="4" max="4" width="13.75" style="3" customWidth="1"/>
     <col min="5" max="5" width="13.5" style="3" customWidth="1"/>
-    <col min="6" max="6" width="57.625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="13.5" style="4" customWidth="1"/>
-    <col min="8" max="8" width="57.625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="21.5" style="4" customWidth="1"/>
+    <col min="6" max="6" width="20.5" style="4" customWidth="1"/>
+    <col min="7" max="7" width="57.625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="13.5" style="4" customWidth="1"/>
+    <col min="9" max="9" width="13.125" style="4" customWidth="1"/>
     <col min="10" max="10" width="57.625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="19.375" style="4" customWidth="1"/>
-    <col min="12" max="12" width="57.75" style="4" customWidth="1"/>
-    <col min="13" max="13" width="19.375" style="4" customWidth="1"/>
-    <col min="14" max="14" width="57.625" style="4" customWidth="1"/>
-    <col min="15" max="15" width="21" style="4" customWidth="1"/>
-    <col min="16" max="16" width="61.625" style="4" customWidth="1"/>
-    <col min="17" max="16384" width="8" style="1"/>
+    <col min="11" max="12" width="21.5" style="4" customWidth="1"/>
+    <col min="13" max="13" width="57.625" style="4" customWidth="1"/>
+    <col min="14" max="14" width="13.5" style="3" customWidth="1"/>
+    <col min="15" max="15" width="20.5" style="4" customWidth="1"/>
+    <col min="16" max="16" width="57.625" style="4" customWidth="1"/>
+    <col min="17" max="17" width="13.5" style="4" customWidth="1"/>
+    <col min="18" max="18" width="13.125" style="4" customWidth="1"/>
+    <col min="19" max="19" width="57.625" style="4" customWidth="1"/>
+    <col min="20" max="21" width="21.5" style="4" customWidth="1"/>
+    <col min="22" max="22" width="57.625" style="4" customWidth="1"/>
+    <col min="23" max="16384" width="8" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16" ht="26.25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:22" ht="26.25" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
@@ -1867,24 +1926,32 @@
       <c r="D2" s="6"/>
       <c r="E2" s="2"/>
       <c r="F2" s="7"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="8"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
       <c r="L2" s="7"/>
       <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
+      <c r="N2" s="2"/>
       <c r="O2" s="7"/>
-      <c r="P2" s="1"/>
-    </row>
-    <row r="3" spans="1:16" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="P2" s="7"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
+    </row>
+    <row r="3" spans="1:22" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="D3" s="11"/>
       <c r="E3" s="12"/>
-      <c r="G3" s="13"/>
-    </row>
-    <row r="4" spans="1:16" s="10" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="H3" s="13"/>
+      <c r="N3" s="12"/>
+      <c r="Q3" s="13"/>
+    </row>
+    <row r="4" spans="1:22" s="10" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="14" t="s">
         <v>1</v>
@@ -1893,9 +1960,14 @@
       <c r="D4" s="15"/>
       <c r="E4" s="2"/>
       <c r="F4" s="14"/>
-      <c r="G4" s="16"/>
-    </row>
-    <row r="5" spans="1:16" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="G4" s="14"/>
+      <c r="H4" s="16"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="16"/>
+    </row>
+    <row r="5" spans="1:22" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5" s="17" t="s">
         <v>2</v>
@@ -1904,9 +1976,14 @@
       <c r="D5" s="11"/>
       <c r="E5" s="18"/>
       <c r="F5" s="17"/>
-      <c r="G5" s="13"/>
-    </row>
-    <row r="6" spans="1:16" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="G5" s="17"/>
+      <c r="H5" s="13"/>
+      <c r="N5" s="18"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="13"/>
+    </row>
+    <row r="6" spans="1:22" s="10" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="B6" s="17" t="s">
         <v>3</v>
@@ -1924,31 +2001,43 @@
       <c r="M6" s="17"/>
       <c r="N6" s="17"/>
       <c r="O6" s="17"/>
-      <c r="P6" s="19"/>
-    </row>
-    <row r="7" spans="1:16" s="10" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+    </row>
+    <row r="7" spans="1:22" s="10" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
-      <c r="E7" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="40"/>
-      <c r="K7" s="40" t="s">
-        <v>5</v>
-      </c>
-      <c r="L7" s="40"/>
-      <c r="M7" s="40"/>
-      <c r="N7" s="40"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
-    </row>
-    <row r="8" spans="1:16" s="10" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E7" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="43"/>
+      <c r="L7" s="43"/>
+      <c r="M7" s="43"/>
+      <c r="N7" s="43" t="s">
+        <v>208</v>
+      </c>
+      <c r="O7" s="43"/>
+      <c r="P7" s="43"/>
+      <c r="Q7" s="43"/>
+      <c r="R7" s="43"/>
+      <c r="S7" s="43"/>
+      <c r="T7" s="43"/>
+      <c r="U7" s="43"/>
+      <c r="V7" s="43"/>
+    </row>
+    <row r="8" spans="1:22" s="10" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
@@ -1956,29 +2045,35 @@
       <c r="E8" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40" t="s">
+      <c r="F8" s="41"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40" t="s">
+      <c r="I8" s="41"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="40"/>
-      <c r="K8" s="40" t="s">
+      <c r="L8" s="39"/>
+      <c r="M8" s="39"/>
+      <c r="N8" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="L8" s="40"/>
-      <c r="M8" s="40" t="s">
+      <c r="O8" s="41"/>
+      <c r="P8" s="42"/>
+      <c r="Q8" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="N8" s="40"/>
-      <c r="O8" s="40" t="s">
+      <c r="R8" s="41"/>
+      <c r="S8" s="42"/>
+      <c r="T8" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="P8" s="40"/>
-    </row>
-    <row r="9" spans="1:16" s="9" customFormat="1" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="U8" s="39"/>
+      <c r="V8" s="39"/>
+    </row>
+    <row r="9" spans="1:22" s="9" customFormat="1" ht="34.5" x14ac:dyDescent="0.3">
       <c r="B9" s="34" t="s">
         <v>9</v>
       </c>
@@ -1992,805 +2087,1039 @@
         <v>204</v>
       </c>
       <c r="F9" s="36" t="s">
+        <v>206</v>
+      </c>
+      <c r="G9" s="36" t="s">
         <v>205</v>
       </c>
-      <c r="G9" s="36" t="s">
+      <c r="H9" s="36" t="s">
         <v>204</v>
       </c>
-      <c r="H9" s="36" t="s">
-        <v>205</v>
-      </c>
       <c r="I9" s="36" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J9" s="36" t="s">
         <v>205</v>
       </c>
       <c r="K9" s="36" t="s">
-        <v>11</v>
+        <v>204</v>
       </c>
       <c r="L9" s="36" t="s">
-        <v>12</v>
+        <v>206</v>
       </c>
       <c r="M9" s="36" t="s">
-        <v>11</v>
+        <v>205</v>
       </c>
       <c r="N9" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="O9" s="37" t="s">
-        <v>11</v>
+        <v>204</v>
+      </c>
+      <c r="O9" s="36" t="s">
+        <v>206</v>
       </c>
       <c r="P9" s="36" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+      <c r="Q9" s="36" t="s">
+        <v>204</v>
+      </c>
+      <c r="R9" s="36" t="s">
+        <v>206</v>
+      </c>
+      <c r="S9" s="36" t="s">
+        <v>205</v>
+      </c>
+      <c r="T9" s="36" t="s">
+        <v>204</v>
+      </c>
+      <c r="U9" s="36" t="s">
+        <v>206</v>
+      </c>
+      <c r="V9" s="36" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B10" s="24" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="L10" s="39"/>
-      <c r="M10" s="39"/>
-      <c r="N10" s="39"/>
-      <c r="O10" s="39"/>
-      <c r="P10" s="39"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="37"/>
+      <c r="O10" s="38"/>
+      <c r="P10" s="38"/>
+      <c r="Q10" s="38"/>
+      <c r="R10" s="38"/>
+      <c r="S10" s="38"/>
+      <c r="T10" s="38"/>
+      <c r="U10" s="38"/>
+      <c r="V10" s="38"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B11" s="24" t="s">
         <v>20</v>
       </c>
       <c r="C11" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="39"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="39"/>
-      <c r="P11" s="39"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="37"/>
+      <c r="O11" s="38"/>
+      <c r="P11" s="38"/>
+      <c r="Q11" s="38"/>
+      <c r="R11" s="38"/>
+      <c r="S11" s="38"/>
+      <c r="T11" s="38"/>
+      <c r="U11" s="38"/>
+      <c r="V11" s="38"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B12" s="24" t="s">
         <v>21</v>
       </c>
       <c r="C12" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="39"/>
-      <c r="P12" s="39"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="38"/>
+      <c r="N12" s="37"/>
+      <c r="O12" s="38"/>
+      <c r="P12" s="38"/>
+      <c r="Q12" s="38"/>
+      <c r="R12" s="38"/>
+      <c r="S12" s="38"/>
+      <c r="T12" s="38"/>
+      <c r="U12" s="38"/>
+      <c r="V12" s="38"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B13" s="24" t="s">
         <v>22</v>
       </c>
       <c r="C13" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="L13" s="39"/>
-      <c r="M13" s="39"/>
-      <c r="N13" s="39"/>
-      <c r="O13" s="39"/>
-      <c r="P13" s="39"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="38"/>
+      <c r="M13" s="38"/>
+      <c r="N13" s="37"/>
+      <c r="O13" s="38"/>
+      <c r="P13" s="38"/>
+      <c r="Q13" s="38"/>
+      <c r="R13" s="38"/>
+      <c r="S13" s="38"/>
+      <c r="T13" s="38"/>
+      <c r="U13" s="38"/>
+      <c r="V13" s="38"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B14" s="24" t="s">
         <v>23</v>
       </c>
       <c r="C14" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="L14" s="39"/>
-      <c r="M14" s="39"/>
-      <c r="N14" s="39"/>
-      <c r="O14" s="39"/>
-      <c r="P14" s="39"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="L14" s="38"/>
+      <c r="M14" s="38"/>
+      <c r="N14" s="37"/>
+      <c r="O14" s="38"/>
+      <c r="P14" s="38"/>
+      <c r="Q14" s="38"/>
+      <c r="R14" s="38"/>
+      <c r="S14" s="38"/>
+      <c r="T14" s="38"/>
+      <c r="U14" s="38"/>
+      <c r="V14" s="38"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B15" s="24" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="39"/>
-      <c r="M15" s="39"/>
-      <c r="N15" s="39"/>
-      <c r="O15" s="39"/>
-      <c r="P15" s="39"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D15" s="37"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="38"/>
+      <c r="M15" s="38"/>
+      <c r="N15" s="37"/>
+      <c r="O15" s="38"/>
+      <c r="P15" s="38"/>
+      <c r="Q15" s="38"/>
+      <c r="R15" s="38"/>
+      <c r="S15" s="38"/>
+      <c r="T15" s="38"/>
+      <c r="U15" s="38"/>
+      <c r="V15" s="38"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B16" s="24" t="s">
         <v>25</v>
       </c>
       <c r="C16" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="39"/>
-      <c r="M16" s="39"/>
-      <c r="N16" s="39"/>
-      <c r="O16" s="39"/>
-      <c r="P16" s="39"/>
-    </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="38"/>
+      <c r="M16" s="38"/>
+      <c r="N16" s="37"/>
+      <c r="O16" s="38"/>
+      <c r="P16" s="38"/>
+      <c r="Q16" s="38"/>
+      <c r="R16" s="38"/>
+      <c r="S16" s="38"/>
+      <c r="T16" s="38"/>
+      <c r="U16" s="38"/>
+      <c r="V16" s="38"/>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B17" s="24" t="s">
         <v>26</v>
       </c>
       <c r="C17" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="39"/>
-      <c r="L17" s="39"/>
-      <c r="M17" s="39"/>
-      <c r="N17" s="39"/>
-      <c r="O17" s="39"/>
-      <c r="P17" s="39"/>
-    </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="38"/>
+      <c r="N17" s="37"/>
+      <c r="O17" s="38"/>
+      <c r="P17" s="38"/>
+      <c r="Q17" s="38"/>
+      <c r="R17" s="38"/>
+      <c r="S17" s="38"/>
+      <c r="T17" s="38"/>
+      <c r="U17" s="38"/>
+      <c r="V17" s="38"/>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B18" s="24" t="s">
         <v>27</v>
       </c>
       <c r="C18" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="39"/>
-      <c r="K18" s="39"/>
-      <c r="L18" s="39"/>
-      <c r="M18" s="39"/>
-      <c r="N18" s="39"/>
-      <c r="O18" s="39"/>
-      <c r="P18" s="39"/>
-    </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="38"/>
+      <c r="M18" s="38"/>
+      <c r="N18" s="37"/>
+      <c r="O18" s="38"/>
+      <c r="P18" s="38"/>
+      <c r="Q18" s="38"/>
+      <c r="R18" s="38"/>
+      <c r="S18" s="38"/>
+      <c r="T18" s="38"/>
+      <c r="U18" s="38"/>
+      <c r="V18" s="38"/>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B19" s="24" t="s">
         <v>28</v>
       </c>
       <c r="C19" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="39"/>
-      <c r="K19" s="39"/>
-      <c r="L19" s="39"/>
-      <c r="M19" s="39"/>
-      <c r="N19" s="39"/>
-      <c r="O19" s="39"/>
-      <c r="P19" s="39"/>
-    </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="38"/>
+      <c r="L19" s="38"/>
+      <c r="M19" s="38"/>
+      <c r="N19" s="37"/>
+      <c r="O19" s="38"/>
+      <c r="P19" s="38"/>
+      <c r="Q19" s="38"/>
+      <c r="R19" s="38"/>
+      <c r="S19" s="38"/>
+      <c r="T19" s="38"/>
+      <c r="U19" s="38"/>
+      <c r="V19" s="38"/>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B20" s="24" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="39"/>
-      <c r="K20" s="39"/>
-      <c r="L20" s="39"/>
-      <c r="M20" s="39"/>
-      <c r="N20" s="39"/>
-      <c r="O20" s="39"/>
-      <c r="P20" s="39"/>
-    </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="38"/>
+      <c r="L20" s="38"/>
+      <c r="M20" s="38"/>
+      <c r="N20" s="37"/>
+      <c r="O20" s="38"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="38"/>
+      <c r="R20" s="38"/>
+      <c r="S20" s="38"/>
+      <c r="T20" s="38"/>
+      <c r="U20" s="38"/>
+      <c r="V20" s="38"/>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B21" s="24" t="s">
         <v>30</v>
       </c>
       <c r="C21" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="39"/>
-      <c r="K21" s="39"/>
-      <c r="L21" s="39"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="39"/>
-      <c r="O21" s="39"/>
-      <c r="P21" s="39"/>
-    </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="38"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="38"/>
+      <c r="N21" s="37"/>
+      <c r="O21" s="38"/>
+      <c r="P21" s="38"/>
+      <c r="Q21" s="38"/>
+      <c r="R21" s="38"/>
+      <c r="S21" s="38"/>
+      <c r="T21" s="38"/>
+      <c r="U21" s="38"/>
+      <c r="V21" s="38"/>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B22" s="24" t="s">
         <v>31</v>
       </c>
       <c r="C22" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="39"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="39"/>
-      <c r="O22" s="39"/>
-      <c r="P22" s="39"/>
-    </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="38"/>
+      <c r="L22" s="38"/>
+      <c r="M22" s="38"/>
+      <c r="N22" s="37"/>
+      <c r="O22" s="38"/>
+      <c r="P22" s="38"/>
+      <c r="Q22" s="38"/>
+      <c r="R22" s="38"/>
+      <c r="S22" s="38"/>
+      <c r="T22" s="38"/>
+      <c r="U22" s="38"/>
+      <c r="V22" s="38"/>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B23" s="24" t="s">
         <v>32</v>
       </c>
       <c r="C23" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="39"/>
-      <c r="K23" s="39"/>
-      <c r="L23" s="39"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="39"/>
-      <c r="O23" s="39"/>
-      <c r="P23" s="39"/>
-    </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="38"/>
+      <c r="M23" s="38"/>
+      <c r="N23" s="37"/>
+      <c r="O23" s="38"/>
+      <c r="P23" s="38"/>
+      <c r="Q23" s="38"/>
+      <c r="R23" s="38"/>
+      <c r="S23" s="38"/>
+      <c r="T23" s="38"/>
+      <c r="U23" s="38"/>
+      <c r="V23" s="38"/>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B24" s="24" t="s">
         <v>33</v>
       </c>
       <c r="C24" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39"/>
-      <c r="K24" s="39"/>
-      <c r="L24" s="39"/>
-      <c r="M24" s="39"/>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-    </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="38"/>
+      <c r="M24" s="38"/>
+      <c r="N24" s="37"/>
+      <c r="O24" s="38"/>
+      <c r="P24" s="38"/>
+      <c r="Q24" s="38"/>
+      <c r="R24" s="38"/>
+      <c r="S24" s="38"/>
+      <c r="T24" s="38"/>
+      <c r="U24" s="38"/>
+      <c r="V24" s="38"/>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B25" s="24" t="s">
         <v>34</v>
       </c>
       <c r="C25" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="39"/>
-      <c r="K25" s="39"/>
-      <c r="L25" s="39"/>
-      <c r="M25" s="39"/>
-      <c r="N25" s="39"/>
-      <c r="O25" s="39"/>
-      <c r="P25" s="39"/>
-    </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
+      <c r="L25" s="38"/>
+      <c r="M25" s="38"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="38"/>
+      <c r="P25" s="38"/>
+      <c r="Q25" s="38"/>
+      <c r="R25" s="38"/>
+      <c r="S25" s="38"/>
+      <c r="T25" s="38"/>
+      <c r="U25" s="38"/>
+      <c r="V25" s="38"/>
+    </row>
+    <row r="26" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B26" s="24" t="s">
         <v>35</v>
       </c>
       <c r="C26" s="31" t="s">
         <v>128</v>
       </c>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="39"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="39"/>
-      <c r="K26" s="39"/>
-      <c r="L26" s="39"/>
-      <c r="M26" s="39"/>
-      <c r="N26" s="39"/>
-      <c r="O26" s="39"/>
-      <c r="P26" s="39"/>
-    </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="38"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="37"/>
+      <c r="O26" s="38"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
+      <c r="S26" s="38"/>
+      <c r="T26" s="38"/>
+      <c r="U26" s="38"/>
+      <c r="V26" s="38"/>
+    </row>
+    <row r="27" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B27" s="24" t="s">
         <v>36</v>
       </c>
       <c r="C27" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="39"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="39"/>
-      <c r="K27" s="39"/>
-      <c r="L27" s="39"/>
-      <c r="M27" s="39"/>
-      <c r="N27" s="39"/>
-      <c r="O27" s="39"/>
-      <c r="P27" s="39"/>
-    </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="38"/>
+      <c r="L27" s="38"/>
+      <c r="M27" s="38"/>
+      <c r="N27" s="37"/>
+      <c r="O27" s="38"/>
+      <c r="P27" s="38"/>
+      <c r="Q27" s="38"/>
+      <c r="R27" s="38"/>
+      <c r="S27" s="38"/>
+      <c r="T27" s="38"/>
+      <c r="U27" s="38"/>
+      <c r="V27" s="38"/>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B28" s="24" t="s">
         <v>37</v>
       </c>
       <c r="C28" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="39"/>
-      <c r="K28" s="39"/>
-      <c r="L28" s="39"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="39"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="39"/>
-    </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="38"/>
+      <c r="K28" s="38"/>
+      <c r="L28" s="38"/>
+      <c r="M28" s="38"/>
+      <c r="N28" s="37"/>
+      <c r="O28" s="38"/>
+      <c r="P28" s="38"/>
+      <c r="Q28" s="38"/>
+      <c r="R28" s="38"/>
+      <c r="S28" s="38"/>
+      <c r="T28" s="38"/>
+      <c r="U28" s="38"/>
+      <c r="V28" s="38"/>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B29" s="24" t="s">
         <v>38</v>
       </c>
       <c r="C29" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="39"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="39"/>
-      <c r="K29" s="39"/>
-      <c r="L29" s="39"/>
-      <c r="M29" s="39"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="39"/>
-    </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="38"/>
+      <c r="J29" s="38"/>
+      <c r="K29" s="38"/>
+      <c r="L29" s="38"/>
+      <c r="M29" s="38"/>
+      <c r="N29" s="37"/>
+      <c r="O29" s="38"/>
+      <c r="P29" s="38"/>
+      <c r="Q29" s="38"/>
+      <c r="R29" s="38"/>
+      <c r="S29" s="38"/>
+      <c r="T29" s="38"/>
+      <c r="U29" s="38"/>
+      <c r="V29" s="38"/>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B30" s="24" t="s">
         <v>39</v>
       </c>
       <c r="C30" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="39"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="39"/>
-      <c r="J30" s="39"/>
-      <c r="K30" s="39"/>
-      <c r="L30" s="39"/>
-      <c r="M30" s="39"/>
-      <c r="N30" s="39"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="39"/>
-    </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
+      <c r="J30" s="38"/>
+      <c r="K30" s="38"/>
+      <c r="L30" s="38"/>
+      <c r="M30" s="38"/>
+      <c r="N30" s="37"/>
+      <c r="O30" s="38"/>
+      <c r="P30" s="38"/>
+      <c r="Q30" s="38"/>
+      <c r="R30" s="38"/>
+      <c r="S30" s="38"/>
+      <c r="T30" s="38"/>
+      <c r="U30" s="38"/>
+      <c r="V30" s="38"/>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B31" s="24" t="s">
         <v>40</v>
       </c>
       <c r="C31" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="D31" s="38"/>
-      <c r="E31" s="38"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="39"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="39"/>
-      <c r="J31" s="39"/>
-      <c r="K31" s="39"/>
-      <c r="L31" s="39"/>
-      <c r="M31" s="39"/>
-      <c r="N31" s="39"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="39"/>
-    </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D31" s="37"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="38"/>
+      <c r="J31" s="38"/>
+      <c r="K31" s="38"/>
+      <c r="L31" s="38"/>
+      <c r="M31" s="38"/>
+      <c r="N31" s="37"/>
+      <c r="O31" s="38"/>
+      <c r="P31" s="38"/>
+      <c r="Q31" s="38"/>
+      <c r="R31" s="38"/>
+      <c r="S31" s="38"/>
+      <c r="T31" s="38"/>
+      <c r="U31" s="38"/>
+      <c r="V31" s="38"/>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B32" s="24" t="s">
         <v>41</v>
       </c>
       <c r="C32" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="D32" s="38"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="39"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="39"/>
-      <c r="J32" s="39"/>
-      <c r="K32" s="39"/>
-      <c r="L32" s="39"/>
-      <c r="M32" s="39"/>
-      <c r="N32" s="39"/>
-      <c r="O32" s="39"/>
-      <c r="P32" s="39"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D32" s="37"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="38"/>
+      <c r="J32" s="38"/>
+      <c r="K32" s="38"/>
+      <c r="L32" s="38"/>
+      <c r="M32" s="38"/>
+      <c r="N32" s="37"/>
+      <c r="O32" s="38"/>
+      <c r="P32" s="38"/>
+      <c r="Q32" s="38"/>
+      <c r="R32" s="38"/>
+      <c r="S32" s="38"/>
+      <c r="T32" s="38"/>
+      <c r="U32" s="38"/>
+      <c r="V32" s="38"/>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B33" s="24" t="s">
         <v>42</v>
       </c>
       <c r="C33" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="D33" s="38"/>
-      <c r="E33" s="38"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="39"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="39"/>
-      <c r="J33" s="39"/>
-      <c r="K33" s="39"/>
-      <c r="L33" s="39"/>
-      <c r="M33" s="39"/>
-      <c r="N33" s="39"/>
-      <c r="O33" s="39"/>
-      <c r="P33" s="39"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D33" s="37"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="38"/>
+      <c r="J33" s="38"/>
+      <c r="K33" s="38"/>
+      <c r="L33" s="38"/>
+      <c r="M33" s="38"/>
+      <c r="N33" s="37"/>
+      <c r="O33" s="38"/>
+      <c r="P33" s="38"/>
+      <c r="Q33" s="38"/>
+      <c r="R33" s="38"/>
+      <c r="S33" s="38"/>
+      <c r="T33" s="38"/>
+      <c r="U33" s="38"/>
+      <c r="V33" s="38"/>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B34" s="24" t="s">
         <v>43</v>
       </c>
       <c r="C34" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="D34" s="38"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="39"/>
-      <c r="J34" s="39"/>
-      <c r="K34" s="39"/>
-      <c r="L34" s="39"/>
-      <c r="M34" s="39"/>
-      <c r="N34" s="39"/>
-      <c r="O34" s="39"/>
-      <c r="P34" s="39"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="38"/>
+      <c r="J34" s="38"/>
+      <c r="K34" s="38"/>
+      <c r="L34" s="38"/>
+      <c r="M34" s="38"/>
+      <c r="N34" s="37"/>
+      <c r="O34" s="38"/>
+      <c r="P34" s="38"/>
+      <c r="Q34" s="38"/>
+      <c r="R34" s="38"/>
+      <c r="S34" s="38"/>
+      <c r="T34" s="38"/>
+      <c r="U34" s="38"/>
+      <c r="V34" s="38"/>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B35" s="24" t="s">
         <v>44</v>
       </c>
       <c r="C35" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="D35" s="38"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="39"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="39"/>
-      <c r="J35" s="39"/>
-      <c r="K35" s="39"/>
-      <c r="L35" s="39"/>
-      <c r="M35" s="39"/>
-      <c r="N35" s="39"/>
-      <c r="O35" s="39"/>
-      <c r="P35" s="39"/>
-    </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D35" s="37"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="38"/>
+      <c r="J35" s="38"/>
+      <c r="K35" s="38"/>
+      <c r="L35" s="38"/>
+      <c r="M35" s="38"/>
+      <c r="N35" s="37"/>
+      <c r="O35" s="38"/>
+      <c r="P35" s="38"/>
+      <c r="Q35" s="38"/>
+      <c r="R35" s="38"/>
+      <c r="S35" s="38"/>
+      <c r="T35" s="38"/>
+      <c r="U35" s="38"/>
+      <c r="V35" s="38"/>
+    </row>
+    <row r="36" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B36" s="24" t="s">
         <v>45</v>
       </c>
       <c r="C36" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="39"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="39"/>
-      <c r="J36" s="39"/>
-      <c r="K36" s="39"/>
-      <c r="L36" s="39"/>
-      <c r="M36" s="39"/>
-      <c r="N36" s="39"/>
-      <c r="O36" s="39"/>
-      <c r="P36" s="39"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D36" s="37"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="38"/>
+      <c r="L36" s="38"/>
+      <c r="M36" s="38"/>
+      <c r="N36" s="37"/>
+      <c r="O36" s="38"/>
+      <c r="P36" s="38"/>
+      <c r="Q36" s="38"/>
+      <c r="R36" s="38"/>
+      <c r="S36" s="38"/>
+      <c r="T36" s="38"/>
+      <c r="U36" s="38"/>
+      <c r="V36" s="38"/>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B37" s="24" t="s">
         <v>46</v>
       </c>
       <c r="C37" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="D37" s="38"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="39"/>
-      <c r="H37" s="39"/>
-      <c r="I37" s="39"/>
-      <c r="J37" s="39"/>
-      <c r="K37" s="39"/>
-      <c r="L37" s="39"/>
-      <c r="M37" s="39"/>
-      <c r="N37" s="39"/>
-      <c r="O37" s="39"/>
-      <c r="P37" s="39"/>
-    </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D37" s="37"/>
+      <c r="E37" s="37"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="38"/>
+      <c r="H37" s="38"/>
+      <c r="I37" s="38"/>
+      <c r="J37" s="38"/>
+      <c r="K37" s="38"/>
+      <c r="L37" s="38"/>
+      <c r="M37" s="38"/>
+      <c r="N37" s="37"/>
+      <c r="O37" s="38"/>
+      <c r="P37" s="38"/>
+      <c r="Q37" s="38"/>
+      <c r="R37" s="38"/>
+      <c r="S37" s="38"/>
+      <c r="T37" s="38"/>
+      <c r="U37" s="38"/>
+      <c r="V37" s="38"/>
+    </row>
+    <row r="38" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B38" s="24" t="s">
         <v>47</v>
       </c>
       <c r="C38" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="39"/>
-      <c r="G38" s="39"/>
-      <c r="H38" s="39"/>
-      <c r="I38" s="39"/>
-      <c r="J38" s="39"/>
-      <c r="K38" s="39"/>
-      <c r="L38" s="39"/>
-      <c r="M38" s="39"/>
-      <c r="N38" s="39"/>
-      <c r="O38" s="39"/>
-      <c r="P38" s="39"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D38" s="37"/>
+      <c r="E38" s="37"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="38"/>
+      <c r="I38" s="38"/>
+      <c r="J38" s="38"/>
+      <c r="K38" s="38"/>
+      <c r="L38" s="38"/>
+      <c r="M38" s="38"/>
+      <c r="N38" s="37"/>
+      <c r="O38" s="38"/>
+      <c r="P38" s="38"/>
+      <c r="Q38" s="38"/>
+      <c r="R38" s="38"/>
+      <c r="S38" s="38"/>
+      <c r="T38" s="38"/>
+      <c r="U38" s="38"/>
+      <c r="V38" s="38"/>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B39" s="24" t="s">
         <v>48</v>
       </c>
       <c r="C39" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="D39" s="38"/>
-      <c r="E39" s="38"/>
-      <c r="F39" s="39"/>
-      <c r="G39" s="39"/>
-      <c r="H39" s="39"/>
-      <c r="I39" s="39"/>
-      <c r="J39" s="39"/>
-      <c r="K39" s="39"/>
-      <c r="L39" s="39"/>
-      <c r="M39" s="39"/>
-      <c r="N39" s="39"/>
-      <c r="O39" s="39"/>
-      <c r="P39" s="39"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D39" s="37"/>
+      <c r="E39" s="37"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="38"/>
+      <c r="I39" s="38"/>
+      <c r="J39" s="38"/>
+      <c r="K39" s="38"/>
+      <c r="L39" s="38"/>
+      <c r="M39" s="38"/>
+      <c r="N39" s="37"/>
+      <c r="O39" s="38"/>
+      <c r="P39" s="38"/>
+      <c r="Q39" s="38"/>
+      <c r="R39" s="38"/>
+      <c r="S39" s="38"/>
+      <c r="T39" s="38"/>
+      <c r="U39" s="38"/>
+      <c r="V39" s="38"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B40" s="24" t="s">
         <v>49</v>
       </c>
       <c r="C40" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="38"/>
-      <c r="E40" s="38"/>
-      <c r="F40" s="39"/>
-      <c r="G40" s="39"/>
-      <c r="H40" s="39"/>
-      <c r="I40" s="39"/>
-      <c r="J40" s="39"/>
-      <c r="K40" s="39"/>
-      <c r="L40" s="39"/>
-      <c r="M40" s="39"/>
-      <c r="N40" s="39"/>
-      <c r="O40" s="39"/>
-      <c r="P40" s="39"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D40" s="37"/>
+      <c r="E40" s="37"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="38"/>
+      <c r="J40" s="38"/>
+      <c r="K40" s="38"/>
+      <c r="L40" s="38"/>
+      <c r="M40" s="38"/>
+      <c r="N40" s="37"/>
+      <c r="O40" s="38"/>
+      <c r="P40" s="38"/>
+      <c r="Q40" s="38"/>
+      <c r="R40" s="38"/>
+      <c r="S40" s="38"/>
+      <c r="T40" s="38"/>
+      <c r="U40" s="38"/>
+      <c r="V40" s="38"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B41" s="24" t="s">
         <v>50</v>
       </c>
       <c r="C41" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="D41" s="38"/>
-      <c r="E41" s="38"/>
-      <c r="F41" s="39"/>
-      <c r="G41" s="39"/>
-      <c r="H41" s="39"/>
-      <c r="I41" s="39"/>
-      <c r="J41" s="39"/>
-      <c r="K41" s="39"/>
-      <c r="L41" s="39"/>
-      <c r="M41" s="39"/>
-      <c r="N41" s="39"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="39"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D41" s="37"/>
+      <c r="E41" s="37"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="38"/>
+      <c r="H41" s="38"/>
+      <c r="I41" s="38"/>
+      <c r="J41" s="38"/>
+      <c r="K41" s="38"/>
+      <c r="L41" s="38"/>
+      <c r="M41" s="38"/>
+      <c r="N41" s="37"/>
+      <c r="O41" s="38"/>
+      <c r="P41" s="38"/>
+      <c r="Q41" s="38"/>
+      <c r="R41" s="38"/>
+      <c r="S41" s="38"/>
+      <c r="T41" s="38"/>
+      <c r="U41" s="38"/>
+      <c r="V41" s="38"/>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B42" s="24" t="s">
         <v>51</v>
       </c>
       <c r="C42" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="D42" s="38"/>
-      <c r="E42" s="38"/>
-      <c r="F42" s="39"/>
-      <c r="G42" s="39"/>
-      <c r="H42" s="39"/>
-      <c r="I42" s="39"/>
-      <c r="J42" s="39"/>
-      <c r="K42" s="39"/>
-      <c r="L42" s="39"/>
-      <c r="M42" s="39"/>
-      <c r="N42" s="39"/>
-      <c r="O42" s="39"/>
-      <c r="P42" s="39"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D42" s="37"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="38"/>
+      <c r="G42" s="38"/>
+      <c r="H42" s="38"/>
+      <c r="I42" s="38"/>
+      <c r="J42" s="38"/>
+      <c r="K42" s="38"/>
+      <c r="L42" s="38"/>
+      <c r="M42" s="38"/>
+      <c r="N42" s="37"/>
+      <c r="O42" s="38"/>
+      <c r="P42" s="38"/>
+      <c r="Q42" s="38"/>
+      <c r="R42" s="38"/>
+      <c r="S42" s="38"/>
+      <c r="T42" s="38"/>
+      <c r="U42" s="38"/>
+      <c r="V42" s="38"/>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B43" s="24" t="s">
         <v>52</v>
       </c>
       <c r="C43" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="D43" s="38"/>
-      <c r="E43" s="38"/>
-      <c r="F43" s="39"/>
-      <c r="G43" s="39"/>
-      <c r="H43" s="39"/>
-      <c r="I43" s="39"/>
-      <c r="J43" s="39"/>
-      <c r="K43" s="39"/>
-      <c r="L43" s="39"/>
-      <c r="M43" s="39"/>
-      <c r="N43" s="39"/>
-      <c r="O43" s="39"/>
-      <c r="P43" s="39"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D43" s="37"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="38"/>
+      <c r="J43" s="38"/>
+      <c r="K43" s="38"/>
+      <c r="L43" s="38"/>
+      <c r="M43" s="38"/>
+      <c r="N43" s="37"/>
+      <c r="O43" s="38"/>
+      <c r="P43" s="38"/>
+      <c r="Q43" s="38"/>
+      <c r="R43" s="38"/>
+      <c r="S43" s="38"/>
+      <c r="T43" s="38"/>
+      <c r="U43" s="38"/>
+      <c r="V43" s="38"/>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B44" s="24" t="s">
         <v>53</v>
       </c>
       <c r="C44" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="D44" s="38"/>
-      <c r="E44" s="38"/>
-      <c r="F44" s="39"/>
-      <c r="G44" s="39"/>
-      <c r="H44" s="39"/>
-      <c r="I44" s="39"/>
-      <c r="J44" s="39"/>
-      <c r="K44" s="39"/>
-      <c r="L44" s="39"/>
-      <c r="M44" s="39"/>
-      <c r="N44" s="39"/>
-      <c r="O44" s="39"/>
-      <c r="P44" s="39"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="38"/>
+      <c r="G44" s="38"/>
+      <c r="H44" s="38"/>
+      <c r="I44" s="38"/>
+      <c r="J44" s="38"/>
+      <c r="K44" s="38"/>
+      <c r="L44" s="38"/>
+      <c r="M44" s="38"/>
+      <c r="N44" s="37"/>
+      <c r="O44" s="38"/>
+      <c r="P44" s="38"/>
+      <c r="Q44" s="38"/>
+      <c r="R44" s="38"/>
+      <c r="S44" s="38"/>
+      <c r="T44" s="38"/>
+      <c r="U44" s="38"/>
+      <c r="V44" s="38"/>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B45" s="24" t="s">
         <v>54</v>
       </c>
       <c r="C45" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="D45" s="38"/>
-      <c r="E45" s="38"/>
-      <c r="F45" s="39"/>
-      <c r="G45" s="39"/>
-      <c r="H45" s="39"/>
-      <c r="I45" s="39"/>
-      <c r="J45" s="39"/>
-      <c r="K45" s="39"/>
-      <c r="L45" s="39"/>
-      <c r="M45" s="39"/>
-      <c r="N45" s="39"/>
-      <c r="O45" s="39"/>
-      <c r="P45" s="39"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="38"/>
+      <c r="G45" s="38"/>
+      <c r="H45" s="38"/>
+      <c r="I45" s="38"/>
+      <c r="J45" s="38"/>
+      <c r="K45" s="38"/>
+      <c r="L45" s="38"/>
+      <c r="M45" s="38"/>
+      <c r="N45" s="37"/>
+      <c r="O45" s="38"/>
+      <c r="P45" s="38"/>
+      <c r="Q45" s="38"/>
+      <c r="R45" s="38"/>
+      <c r="S45" s="38"/>
+      <c r="T45" s="38"/>
+      <c r="U45" s="38"/>
+      <c r="V45" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="E7:J7"/>
-    <mergeCell ref="K7:P7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="N7:V7"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="T8:V8"/>
+    <mergeCell ref="E7:M7"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:J8"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2903,52 +3232,52 @@
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
-      <c r="E7" s="40" t="s">
+      <c r="E7" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="40"/>
-      <c r="K7" s="40" t="s">
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="L7" s="40"/>
-      <c r="M7" s="40"/>
-      <c r="N7" s="40"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
+      <c r="L7" s="39"/>
+      <c r="M7" s="39"/>
+      <c r="N7" s="39"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="39"/>
     </row>
     <row r="8" spans="1:16" s="10" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
-      <c r="E8" s="40" t="s">
+      <c r="E8" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40" t="s">
+      <c r="F8" s="39"/>
+      <c r="G8" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40" t="s">
+      <c r="H8" s="39"/>
+      <c r="I8" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="40"/>
-      <c r="K8" s="40" t="s">
+      <c r="J8" s="39"/>
+      <c r="K8" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="L8" s="40"/>
-      <c r="M8" s="40" t="s">
+      <c r="L8" s="39"/>
+      <c r="M8" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="N8" s="40"/>
-      <c r="O8" s="40" t="s">
+      <c r="N8" s="39"/>
+      <c r="O8" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="P8" s="40"/>
+      <c r="P8" s="39"/>
     </row>
     <row r="9" spans="1:16" s="9" customFormat="1" ht="35.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="20" t="s">
